--- a/_work/analysis/02_сравнение_займ.xlsx
+++ b/_work/analysis/02_сравнение_займ.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Остатки чужих данных" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Статус и полнота чтения" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Проверка цитат" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Поправки (этап 3)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,6 +76,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15383,4 +15390,97 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>При подготовке этапа 3 найдены неточности этапа 2. Лист «Сравнение» не переписан: читайте его вместе с этим листом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Было в таблице этапа 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Исправление (по исходному тексту)</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Как проверено</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Персональные данные/конфиденциальность/согласия</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>в №11, №12 положения о праве Поверенного обрабатывать персональные данные нет</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>есть: «6.6.3. Производить обработку персональных данных Заемщика» — №11 Алматы ИП п. 6.6.3, №12 Алматы СПК п. 6.6.3</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>grep по _work/text/, этап 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Основания досрочного истребования/расторжения; Права займодателя</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ВКО — только судебный порядок обращения взыскания</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>в займе №19 п. 7.4 и в залогах ВКО №17/№18 судебный порядок только в русском тексте; в казахском тексте залогов №17/№18 — «сот және соттан тыс» (судебный и внесудебный); это также расхождение каз./рус.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>grep по _work/text/, этап 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/_work/analysis/02_сравнение_займ.xlsx
+++ b/_work/analysis/02_сравнение_займ.xlsx
@@ -15398,7 +15398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15480,6 +15480,72 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Права займодателя (запреты)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>у №11 раздела «Займодатель не вправе» нет</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>есть: №11 пп. 6.5.1–6.5.5</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>поиск по тексту, этап 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Уведомления</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>№25, №37 — без «под роспись»; №47 только «с момента отправки»</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>в №25 (п. 10.1) и №37 (11.1) «под роспись» есть; в №47 пп. 10.3 и 11.6 противоречат друг другу (внутренний дефект)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>поиск по тексту, этап 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Особое условие: переуступка прав и правопреемство</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>№15 — запрета на передачу прав нет</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>№15 п. 6.2.1 — Заемщик обязан не передавать права и обязанности третьим лицам</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>поиск по тексту, этап 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
